--- a/04_BOM/RP1_BOM_7DOF_MotionHead.xlsx
+++ b/04_BOM/RP1_BOM_7DOF_MotionHead.xlsx
@@ -233,7 +233,7 @@
     <t xml:space="preserve">YCL.M000331</t>
   </si>
   <si>
-    <t xml:space="preserve">雷赛灵巧手转接件</t>
+    <t xml:space="preserve">灵巧手转接件</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.M000332</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">模组</t>
   </si>
   <si>
-    <t xml:space="preserve">雷赛电机模组 PJ3-60CAN29</t>
+    <t xml:space="preserve">电机模组 PJ3-60CAN29</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.D000040</t>
   </si>
   <si>
-    <t xml:space="preserve">雷赛电机模组 PJ2-55CAN25</t>
+    <t xml:space="preserve">电机模组 PJ2-55CAN25</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.E000211</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">YCL.D000003</t>
   </si>
   <si>
-    <t xml:space="preserve">雷赛电机模组 PJ3-75CAN42</t>
+    <t xml:space="preserve">电机模组 PJ3-75CAN42</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.D000001</t>
   </si>
   <si>
-    <t xml:space="preserve">雷赛电机模组 PJ3-97CAN140</t>
+    <t xml:space="preserve">电机模组 PJ3-97CAN140</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.E000057</t>

--- a/04_BOM/RP1_BOM_7DOF_MotionHead.xlsx
+++ b/04_BOM/RP1_BOM_7DOF_MotionHead.xlsx
@@ -233,7 +233,7 @@
     <t xml:space="preserve">YCL.M000331</t>
   </si>
   <si>
-    <t xml:space="preserve">灵巧手转接件</t>
+    <t xml:space="preserve">RP_Hand转接件</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.M000332</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">模组</t>
   </si>
   <si>
-    <t xml:space="preserve">电机模组 PJ3-60CAN29</t>
+    <t xml:space="preserve">电机模组 RMM6562-2E</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.D000040</t>
   </si>
   <si>
-    <t xml:space="preserve">电机模组 PJ2-55CAN25</t>
+    <t xml:space="preserve">电机模组 RZW5552-2C</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.E000211</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">YCL.D000003</t>
   </si>
   <si>
-    <t xml:space="preserve">电机模组 PJ3-75CAN42</t>
+    <t xml:space="preserve">电机模组 RMM8463-2E</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.D000001</t>
   </si>
   <si>
-    <t xml:space="preserve">电机模组 PJ3-97CAN140</t>
+    <t xml:space="preserve">电机模组 RMM10062-2E</t>
   </si>
   <si>
     <t xml:space="preserve">YCL.E000057</t>

--- a/04_BOM/RP1_BOM_7DOF_MotionHead.xlsx
+++ b/04_BOM/RP1_BOM_7DOF_MotionHead.xlsx
@@ -473,7 +473,7 @@
     <t xml:space="preserve">轴承钢</t>
   </si>
   <si>
-    <t xml:space="preserve">YCL.D000002</t>
+    <t xml:space="preserve">YCL.D000020</t>
   </si>
   <si>
     <t xml:space="preserve">模组</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">电机模组 RMM6562-2E</t>
   </si>
   <si>
-    <t xml:space="preserve">YCL.D000040</t>
+    <t xml:space="preserve">YCL.D000048</t>
   </si>
   <si>
     <t xml:space="preserve">电机模组 RZW5552-2C</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">深沟球轴承61804-2RS</t>
   </si>
   <si>
-    <t xml:space="preserve">YCL.D000003</t>
+    <t xml:space="preserve">YCL.D000027</t>
   </si>
   <si>
     <t xml:space="preserve">电机模组 RMM8463-2E</t>
   </si>
   <si>
-    <t xml:space="preserve">YCL.D000001</t>
+    <t xml:space="preserve">YCL.D000031</t>
   </si>
   <si>
     <t xml:space="preserve">电机模组 RMM10062-2E</t>
